--- a/premise/data/additional_inventories/lci-syngas.xlsx
+++ b/premise/data/additional_inventories/lci-syngas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9D54B4-BADF-514A-8141-66591AFC306C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9335087C-0DE7-074B-A55F-D99D28930307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="1480" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Syngas" sheetId="1" r:id="rId1"/>
@@ -518,12 +518,6 @@
     <t>electricity production, from combined cycle plant, synthetic natural gas, post, pipeline 200km, storage 1000m/RER U</t>
   </si>
   <si>
-    <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from grid electricity</t>
-  </si>
-  <si>
-    <t>hydrogen, gaseous, 30 bar</t>
-  </si>
-  <si>
     <t>carbon dioxide, captured at synthetic natural gas plant, post, 200km pipeline, storage 1000m</t>
   </si>
   <si>
@@ -588,6 +582,12 @@
   </si>
   <si>
     <t>carbon dioxide, captured</t>
+  </si>
+  <si>
+    <t>market for hydrogen, gaseous, low pressure</t>
+  </si>
+  <si>
+    <t>hydrogen, gaseous, low pressure</t>
   </si>
 </sst>
 </file>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="36" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B36" s="5">
         <f>3.6/0.62/47.5</f>
@@ -1889,7 +1889,7 @@
         <v>39</v>
       </c>
       <c r="L37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -1924,7 +1924,7 @@
         <v>36</v>
       </c>
       <c r="L38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -2032,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -2857,7 +2857,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B77">
         <f>B78*2.65*0.9</f>
@@ -2885,12 +2885,12 @@
         <v>43</v>
       </c>
       <c r="M77" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B78" s="5">
         <f>3.6/0.54/47.5</f>
@@ -2941,7 +2941,7 @@
         <v>41</v>
       </c>
       <c r="M79" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
@@ -2973,7 +2973,7 @@
         <v>39</v>
       </c>
       <c r="M80" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
@@ -3008,7 +3008,7 @@
         <v>36</v>
       </c>
       <c r="M81" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
@@ -3116,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="M84" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
@@ -3148,7 +3148,7 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
@@ -3295,7 +3295,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B98" s="15">
         <f>((B97*1000)-(600*3.78541/1000))/1000</f>
@@ -3305,18 +3305,18 @@
         <v>98</v>
       </c>
       <c r="E98" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F98" t="s">
         <v>24</v>
       </c>
       <c r="J98" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -3371,13 +3371,13 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B101">
         <v>0.38400000000000001</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D101" t="s">
         <v>25</v>
@@ -3398,7 +3398,7 @@
         <v>96</v>
       </c>
       <c r="K101" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.2">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="122" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B122" s="7">
         <v>1</v>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="124" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B124" s="8">
         <f>1.972/0.717</f>
@@ -3984,7 +3984,7 @@
         <v>22</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I124" s="7">
         <v>2</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="125" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B125" s="8">
         <f>(4*0.0893)/0.717</f>
@@ -4038,7 +4038,7 @@
         <v>22</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I125" s="7">
         <v>2</v>
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K128" s="8"/>
       <c r="L128" s="8"/>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="138" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B138" s="7">
         <v>1</v>
@@ -4415,7 +4415,7 @@
     </row>
     <row r="140" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B140" s="8">
         <f>1.972/0.717</f>
@@ -4431,7 +4431,7 @@
         <v>22</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I140" s="7">
         <v>2</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="141" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B141" s="8">
         <f>(4*0.0893)/0.717</f>
@@ -4485,7 +4485,7 @@
         <v>22</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I141" s="7">
         <v>2</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="154" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B154" s="7">
         <v>1</v>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="156" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B156" s="8">
         <f>1.972/0.717</f>
@@ -4878,7 +4878,7 @@
         <v>22</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I156" s="7">
         <v>2</v>
@@ -4916,7 +4916,7 @@
     </row>
     <row r="157" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B157" s="8">
         <f>(4*0.0893)/0.717</f>
@@ -4932,7 +4932,7 @@
         <v>22</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I157" s="7">
         <v>2</v>
@@ -5309,7 +5309,7 @@
     </row>
     <row r="172" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B172" s="7">
         <f>1.972/0.717</f>
@@ -5325,7 +5325,7 @@
         <v>22</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I172" s="7">
         <v>2</v>
@@ -5363,7 +5363,7 @@
     </row>
     <row r="173" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B173" s="7">
         <f>(4*0.0893)/0.717</f>
@@ -5379,7 +5379,7 @@
         <v>22</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I173" s="7">
         <v>2</v>
@@ -5756,7 +5756,7 @@
     </row>
     <row r="188" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B188" s="7">
         <f>1.972/0.717</f>
@@ -5772,7 +5772,7 @@
         <v>22</v>
       </c>
       <c r="G188" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I188" s="7">
         <v>2</v>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="189" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B189" s="7">
         <f>(4*0.0893)/0.717</f>
@@ -5826,7 +5826,7 @@
         <v>22</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I189" s="7">
         <v>2</v>
@@ -5928,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K192" s="8"/>
       <c r="L192" s="8"/>
@@ -6141,7 +6141,7 @@
     </row>
     <row r="203" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B203" s="7">
         <v>2.75</v>
@@ -6156,7 +6156,7 @@
         <v>22</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I203" s="7">
         <v>2</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="204" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B204" s="7">
         <v>0.5</v>
@@ -6219,7 +6219,7 @@
         <v>22</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I204" s="7">
         <v>2</v>
@@ -6663,7 +6663,7 @@
     </row>
     <row r="220" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B220" s="7">
         <v>2.75</v>
@@ -6678,7 +6678,7 @@
         <v>22</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I220" s="7">
         <v>2</v>
@@ -6726,7 +6726,7 @@
     </row>
     <row r="221" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B221" s="7">
         <v>0.5</v>
@@ -6741,7 +6741,7 @@
         <v>22</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I221" s="7">
         <v>2</v>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="237" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B237" s="7">
         <v>2.75</v>
@@ -7200,7 +7200,7 @@
         <v>22</v>
       </c>
       <c r="G237" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I237" s="7">
         <v>2</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="238" spans="1:20" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" s="11" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B238" s="7">
         <v>0.5</v>
@@ -7263,7 +7263,7 @@
         <v>22</v>
       </c>
       <c r="G238" s="7" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I238" s="7">
         <v>2</v>
